--- a/course_evaluation_forms/008_geology_course_feedback_survey--course_evaluation_forms.xlsx
+++ b/course_evaluation_forms/008_geology_course_feedback_survey--course_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -807,8 +807,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,12 +836,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'highly_satisfactory'}</t>
+          <t>highly_satisfactory</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Satisfactory'}</t>
+          <t>Highly Satisfactory</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'satisfactory'}</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Satisfactory'}</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': '1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'4-5'}</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': '4-5'}</t>
+          <t>4-5</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'3-5'}</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': '3-5'}</t>
+          <t>3-5</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'2-5'}</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': '2-5'}</t>
+          <t>2-5</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'1-4'}</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': '1-4'}</t>
+          <t>1-4</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'geology'}</t>
+          <t>geology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'geology'}</t>
+          <t>geology</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'highly_recommended'}</t>
+          <t>highly_recommended</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Highly Recommended'}</t>
+          <t>Highly Recommended</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'not_recommended'}</t>
+          <t>not_recommended</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Not Recommended'}</t>
+          <t>Not Recommended</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
